--- a/Employee.xlsx
+++ b/Employee.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11210"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dgerbing/Documents/BookNew/data/Employee/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidgerbing/Documents/BookNew/data/Employee/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56314E9E-8960-3347-8964-C91A7439C7C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F886EE61-58D7-B444-A327-F9BCAC71B2B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25380" yWindow="4420" windowWidth="24300" windowHeight="20440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="d" sheetId="1" r:id="rId1"/>
@@ -194,7 +194,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -207,6 +211,13 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -240,27 +251,26 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -558,41 +568,42 @@
   <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" customWidth="1"/>
     <col min="2" max="2" width="5.6640625" customWidth="1"/>
-    <col min="3" max="3" width="6" style="6" customWidth="1"/>
-    <col min="4" max="4" width="6" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.6640625" customWidth="1"/>
+    <col min="3" max="3" width="6.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="6.6640625" style="3" customWidth="1"/>
-    <col min="7" max="9" width="4.1640625" customWidth="1"/>
+    <col min="7" max="7" width="5.1640625" style="3" customWidth="1"/>
+    <col min="8" max="9" width="5.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="5" t="s">
         <v>7</v>
       </c>
     </row>
@@ -603,19 +614,19 @@
       <c r="B2">
         <v>7</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="4">
-        <v>53788.26</v>
+        <v>63788.26</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="3">
         <v>1</v>
       </c>
       <c r="H2">
@@ -629,19 +640,19 @@
       <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="C3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="4">
-        <v>94494.58</v>
+        <v>104494.58</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="3">
         <v>1</v>
       </c>
       <c r="H3">
@@ -658,19 +669,19 @@
       <c r="B4">
         <v>7</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="C4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
         <v>17</v>
       </c>
       <c r="E4" s="4">
-        <v>57139.9</v>
+        <v>67139.899999999994</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="3">
         <v>2</v>
       </c>
       <c r="H4">
@@ -687,19 +698,19 @@
       <c r="B5">
         <v>15</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="C5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="4">
-        <v>111074.86</v>
+        <v>121074.86</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="3">
         <v>3</v>
       </c>
       <c r="H5">
@@ -716,13 +727,13 @@
       <c r="B6">
         <v>5</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E6" s="4">
-        <v>53772.58</v>
-      </c>
-      <c r="G6">
+        <v>63772.58</v>
+      </c>
+      <c r="G6" s="3">
         <v>1</v>
       </c>
       <c r="H6">
@@ -739,19 +750,19 @@
       <c r="B7">
         <v>6</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="3" t="s">
+      <c r="C7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="4">
-        <v>69441.929999999993</v>
+        <v>79441.929999999993</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="3">
         <v>2</v>
       </c>
       <c r="H7">
@@ -768,19 +779,19 @@
       <c r="B8">
         <v>18</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="3" t="s">
+      <c r="C8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" t="s">
         <v>23</v>
       </c>
       <c r="E8" s="4">
-        <v>99062.66</v>
+        <v>109062.66</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="3">
         <v>3</v>
       </c>
       <c r="H8">
@@ -797,19 +808,19 @@
       <c r="B9">
         <v>8</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="3" t="s">
+      <c r="C9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" t="s">
         <v>13</v>
       </c>
       <c r="E9" s="4">
-        <v>72321.36</v>
+        <v>82321.36</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="3">
         <v>1</v>
       </c>
       <c r="H9">
@@ -826,19 +837,19 @@
       <c r="B10">
         <v>8</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="3" t="s">
+      <c r="C10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" t="s">
         <v>23</v>
       </c>
       <c r="E10" s="4">
-        <v>61356.69</v>
+        <v>71356.69</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="3">
         <v>2</v>
       </c>
       <c r="H10">
@@ -855,19 +866,19 @@
       <c r="B11">
         <v>4</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="3" t="s">
+      <c r="C11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" t="s">
         <v>23</v>
       </c>
       <c r="E11" s="4">
-        <v>56772.95</v>
+        <v>66772.95</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="3">
         <v>1</v>
       </c>
       <c r="H11">
@@ -884,19 +895,19 @@
       <c r="B12">
         <v>8</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="3" t="s">
+      <c r="C12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" t="s">
         <v>13</v>
       </c>
       <c r="E12" s="4">
-        <v>55545.25</v>
+        <v>65545.25</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="3">
         <v>1</v>
       </c>
       <c r="H12">
@@ -913,19 +924,19 @@
       <c r="B13">
         <v>13</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="3" t="s">
+      <c r="C13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" t="s">
         <v>13</v>
       </c>
       <c r="E13" s="4">
-        <v>81871.05</v>
+        <v>91871.05</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="3">
         <v>2</v>
       </c>
       <c r="H13">
@@ -942,19 +953,19 @@
       <c r="B14">
         <v>9</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="3" t="s">
+      <c r="C14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" t="s">
         <v>30</v>
       </c>
       <c r="E14" s="4">
-        <v>71084.02</v>
+        <v>81084.02</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="3">
         <v>2</v>
       </c>
       <c r="H14">
@@ -971,19 +982,19 @@
       <c r="B15">
         <v>10</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="3" t="s">
+      <c r="C15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="4">
-        <v>66337.83</v>
+        <v>76337.83</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="3">
         <v>1</v>
       </c>
       <c r="H15">
@@ -1000,19 +1011,19 @@
       <c r="B16">
         <v>14</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="3" t="s">
+      <c r="C16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" t="s">
         <v>17</v>
       </c>
       <c r="E16" s="4">
-        <v>95027.55</v>
+        <v>105027.55</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="3">
         <v>3</v>
       </c>
       <c r="H16">
@@ -1029,19 +1040,19 @@
       <c r="B17">
         <v>10</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" s="3" t="s">
+      <c r="C17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" t="s">
         <v>13</v>
       </c>
       <c r="E17" s="4">
-        <v>92681.19</v>
+        <v>102681.19</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="3">
         <v>2</v>
       </c>
       <c r="H17">
@@ -1058,19 +1069,19 @@
       <c r="B18">
         <v>18</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18" s="3" t="s">
+      <c r="C18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" t="s">
         <v>23</v>
       </c>
       <c r="E18" s="4">
-        <v>91352.33</v>
+        <v>101352.33</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="3">
         <v>2</v>
       </c>
       <c r="H18">
@@ -1087,19 +1098,19 @@
       <c r="B19">
         <v>21</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="3" t="s">
+      <c r="C19" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" t="s">
         <v>13</v>
       </c>
       <c r="E19" s="4">
-        <v>134419.23000000001</v>
+        <v>144419.23000000001</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="3">
         <v>1</v>
       </c>
       <c r="H19">
@@ -1116,19 +1127,19 @@
       <c r="B20">
         <v>18</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D20" s="3" t="s">
+      <c r="C20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" t="s">
         <v>10</v>
       </c>
       <c r="E20" s="4">
-        <v>122563.38</v>
+        <v>132563.38</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="3">
         <v>3</v>
       </c>
       <c r="H20">
@@ -1145,19 +1156,19 @@
       <c r="B21">
         <v>5</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="3" t="s">
+      <c r="C21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" t="s">
         <v>30</v>
       </c>
       <c r="E21" s="4">
-        <v>49704.79</v>
+        <v>59704.79</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="3">
         <v>3</v>
       </c>
       <c r="H21">
@@ -1174,19 +1185,19 @@
       <c r="B22">
         <v>14</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="3" t="s">
+      <c r="C22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" t="s">
         <v>13</v>
       </c>
       <c r="E22" s="4">
-        <v>83014.429999999993</v>
+        <v>93014.43</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="3">
         <v>2</v>
       </c>
       <c r="H22">
@@ -1203,19 +1214,19 @@
       <c r="B23">
         <v>3</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D23" s="3" t="s">
+      <c r="C23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" t="s">
         <v>13</v>
       </c>
       <c r="E23" s="4">
-        <v>49868.68</v>
+        <v>59868.68</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="3">
         <v>2</v>
       </c>
       <c r="H23">
@@ -1232,19 +1243,19 @@
       <c r="B24">
         <v>9</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="3" t="s">
+      <c r="C24" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" t="s">
         <v>13</v>
       </c>
       <c r="E24" s="4">
-        <v>69624.87</v>
+        <v>79624.87</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="3">
         <v>1</v>
       </c>
       <c r="H24">
@@ -1261,19 +1272,19 @@
       <c r="B25">
         <v>10</v>
       </c>
-      <c r="C25" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="3" t="s">
+      <c r="C25" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" t="s">
         <v>17</v>
       </c>
       <c r="E25" s="4">
-        <v>66312.89</v>
+        <v>76312.89</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="3">
         <v>1</v>
       </c>
       <c r="H25">
@@ -1290,19 +1301,19 @@
       <c r="B26">
         <v>13</v>
       </c>
-      <c r="C26" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="3" t="s">
+      <c r="C26" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" t="s">
         <v>13</v>
       </c>
       <c r="E26" s="4">
-        <v>77714.850000000006</v>
+        <v>87714.85</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="3">
         <v>1</v>
       </c>
       <c r="H26">
@@ -1319,19 +1330,19 @@
       <c r="B27">
         <v>5</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="3" t="s">
+      <c r="C27" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" t="s">
         <v>13</v>
       </c>
       <c r="E27" s="4">
-        <v>49188.959999999999</v>
+        <v>59188.959999999999</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="3">
         <v>3</v>
       </c>
       <c r="H27">
@@ -1348,19 +1359,19 @@
       <c r="B28">
         <v>3</v>
       </c>
-      <c r="C28" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D28" s="3" t="s">
+      <c r="C28" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D28" t="s">
         <v>30</v>
       </c>
       <c r="E28" s="4">
-        <v>46124.97</v>
+        <v>56124.97</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="3">
         <v>2</v>
       </c>
       <c r="H28">
@@ -1377,19 +1388,19 @@
       <c r="B29">
         <v>2</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D29" s="3" t="s">
+      <c r="C29" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29" t="s">
         <v>10</v>
       </c>
       <c r="E29" s="4">
-        <v>61055.44</v>
+        <v>71055.44</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="3">
         <v>2</v>
       </c>
       <c r="H29">
@@ -1406,19 +1417,19 @@
       <c r="B30">
         <v>9</v>
       </c>
-      <c r="C30" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" s="3" t="s">
+      <c r="C30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" t="s">
         <v>30</v>
       </c>
       <c r="E30" s="4">
-        <v>69547.600000000006</v>
+        <v>79547.600000000006</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G30">
+      <c r="G30" s="3">
         <v>1</v>
       </c>
       <c r="H30">
@@ -1435,19 +1446,19 @@
       <c r="B31">
         <v>13</v>
       </c>
-      <c r="C31" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="3" t="s">
+      <c r="C31" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" t="s">
         <v>13</v>
       </c>
       <c r="E31" s="4">
-        <v>87785.51</v>
+        <v>97785.51</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G31">
+      <c r="G31" s="3">
         <v>1</v>
       </c>
       <c r="H31">
@@ -1464,16 +1475,16 @@
       <c r="B32">
         <v>2</v>
       </c>
-      <c r="C32" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D32" s="3" t="s">
+      <c r="C32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32" t="s">
         <v>30</v>
       </c>
       <c r="E32" s="4">
-        <v>72502.5</v>
-      </c>
-      <c r="G32">
+        <v>82502.5</v>
+      </c>
+      <c r="G32" s="3">
         <v>2</v>
       </c>
       <c r="H32">
@@ -1490,19 +1501,19 @@
       <c r="B33">
         <v>10</v>
       </c>
-      <c r="C33" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D33" s="3" t="s">
+      <c r="C33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D33" t="s">
         <v>23</v>
       </c>
       <c r="E33" s="4">
-        <v>61961.29</v>
+        <v>71961.289999999994</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G33">
+      <c r="G33" s="3">
         <v>2</v>
       </c>
       <c r="H33">
@@ -1519,19 +1530,19 @@
       <c r="B34">
         <v>4</v>
       </c>
-      <c r="C34" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D34" s="3" t="s">
+      <c r="C34" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D34" t="s">
         <v>10</v>
       </c>
       <c r="E34" s="4">
-        <v>72675.259999999995</v>
+        <v>82675.259999999995</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G34">
+      <c r="G34" s="3">
         <v>2</v>
       </c>
       <c r="H34">
@@ -1548,19 +1559,19 @@
       <c r="B35">
         <v>24</v>
       </c>
-      <c r="C35" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="3" t="s">
+      <c r="C35" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" t="s">
         <v>10</v>
       </c>
       <c r="E35" s="4">
-        <v>108138.43</v>
+        <v>118138.43</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G35">
+      <c r="G35" s="3">
         <v>2</v>
       </c>
       <c r="H35">
@@ -1577,19 +1588,19 @@
       <c r="B36">
         <v>1</v>
       </c>
-      <c r="C36" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D36" s="3" t="s">
+      <c r="C36" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D36" t="s">
         <v>23</v>
       </c>
       <c r="E36" s="4">
-        <v>51036.85</v>
+        <v>61036.85</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G36">
+      <c r="G36" s="3">
         <v>2</v>
       </c>
       <c r="H36">
@@ -1606,19 +1617,19 @@
       <c r="B37">
         <v>2</v>
       </c>
-      <c r="C37" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D37" s="3" t="s">
+      <c r="C37" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D37" t="s">
         <v>13</v>
       </c>
       <c r="E37" s="4">
-        <v>56508.32</v>
+        <v>66508.320000000007</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G37">
+      <c r="G37" s="3">
         <v>2</v>
       </c>
       <c r="H37">
@@ -1635,19 +1646,19 @@
       <c r="B38">
         <v>10</v>
       </c>
-      <c r="C38" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="3" t="s">
+      <c r="C38" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" t="s">
         <v>17</v>
       </c>
       <c r="E38" s="4">
-        <v>57562.36</v>
+        <v>67562.36</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G38">
+      <c r="G38" s="3">
         <v>1</v>
       </c>
       <c r="H38">
